--- a/Login.xlsx
+++ b/Login.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30210"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{81C0A962-5C84-475D-986E-6FA8B6186F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{868DB295-0D85-441D-93D9-14C36D2DA80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="login" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
   <si>
     <t>Username</t>
   </si>
@@ -45,6 +45,12 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>Employee Name</t>
+  </si>
+  <si>
     <t>manager</t>
   </si>
   <si>
@@ -57,12 +63,24 @@
     <t>AD_Tools Team</t>
   </si>
   <si>
+    <t>EMP007</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
     <t>srm</t>
   </si>
   <si>
     <t>srm123</t>
   </si>
   <si>
+    <t>EMP008</t>
+  </si>
+  <si>
+    <t>SRM</t>
+  </si>
+  <si>
     <t>rishika</t>
   </si>
   <si>
@@ -72,6 +90,12 @@
     <t>Team Member</t>
   </si>
   <si>
+    <t>EMP009</t>
+  </si>
+  <si>
+    <t>Rishika</t>
+  </si>
+  <si>
     <t xml:space="preserve">                                                                      </t>
   </si>
   <si>
@@ -79,6 +103,84 @@
   </si>
   <si>
     <t>sona123</t>
+  </si>
+  <si>
+    <t>EMP010</t>
+  </si>
+  <si>
+    <t>Sona</t>
+  </si>
+  <si>
+    <t>sivasree</t>
+  </si>
+  <si>
+    <t>sivasree123</t>
+  </si>
+  <si>
+    <t>EMP001</t>
+  </si>
+  <si>
+    <t>Sivasree MR</t>
+  </si>
+  <si>
+    <t>porkodi</t>
+  </si>
+  <si>
+    <t>porkodi123</t>
+  </si>
+  <si>
+    <t>EMP002</t>
+  </si>
+  <si>
+    <t>Porkodi S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yamini </t>
+  </si>
+  <si>
+    <t>yamini123</t>
+  </si>
+  <si>
+    <t>EMP003</t>
+  </si>
+  <si>
+    <t>Yamini S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sundar </t>
+  </si>
+  <si>
+    <t>sundar123</t>
+  </si>
+  <si>
+    <t>EMP004</t>
+  </si>
+  <si>
+    <t>Sundar G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">santhosh </t>
+  </si>
+  <si>
+    <t>santhosh123</t>
+  </si>
+  <si>
+    <t>EMP005</t>
+  </si>
+  <si>
+    <t>Santhosh U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">priyadarshini </t>
+  </si>
+  <si>
+    <t>priyadarshini123</t>
+  </si>
+  <si>
+    <t>EMP006</t>
+  </si>
+  <si>
+    <t>Priyadarshini T</t>
   </si>
 </sst>
 </file>
@@ -446,16 +548,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16.125" customWidth="1"/>
     <col min="2" max="2" width="11.625" customWidth="1"/>
     <col min="3" max="3" width="18.875" customWidth="1"/>
     <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -468,66 +572,217 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.75">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75">
       <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="J4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75">
+      <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75">
+      <c r="A7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75">
+      <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75">
+      <c r="A9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75">
+      <c r="A10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.75">
+      <c r="A11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
